--- a/data/trans_bre/IP1016-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1016-Habitat-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,0</t>
+          <t>-0,53; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
